--- a/data_extactor/batch_10_fa/batch_0071_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0071_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخنرانی</t>
+          <t>سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید غذا | زیست‌شناسی | زبان انگلیسی | مکانیک | ایمنی و امنیت عمومی | شیمی</t>
+          <t>تولید مواد غذایی | زیست‌شناسی | زبان انگلیسی | مکانیک | ایمنی و امنیت عمومی | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>قدرت تنه | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه حرکت | زبردستی دستی | هماهنگی چند عضو | زبردستی انگشتان | قدرت ایستا | قدرت پویا | کنترل نرخ | بینایی نزدیک | استقامت | قدرت انفجاری | بیان شفاهی | زمان واکنش | درک شفاهی | بینایی دور | هماهنگی کلی بدن | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | استدلال قیاسی | حساسیت به مشکلات</t>
+          <t>قدرت تنه | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه حرکت | مهارت دستی | هماهنگی چند عضو | مهارت انگشتان | قدرت ایستا | قدرت پویا | کنترل نرخ | بینایی نزدیک | استقامت | قدرت انفجاری | بیان شفاهی | زمان عکس‌العمل | درک شفاهی | بینایی دور | هماهنگی کلی بدن | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دمای بسیار گرم یا سرد | فشار زمانی | صرف زمان به صورت ایستاده | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای پیاده‌روی یا دویدن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | صرف زمان برای ایستادن | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پرداخت | قطع‌کنندگان درختان | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سازندگان دسته‌ای مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | کارگران جنگل و حفاظت | درجه‌بندی‌کنندگان و سورترهای محصولات کشاورزی | کارگران ساده و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران محوطه‌سازی و فضای سبز | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کنترل‌کنندگان، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش‌ها، پوشش گیاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | دانشمندان خاک و گیاه | هرس‌کنندگان و آرایش‌دهندگان درختان</t>
+          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | قطع‌کنندگان درختان | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | کارگران جنگل و حفاظت | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران فضای سبز و نگهداری محوطه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بندهای دستی | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | دانشمندان خاک و گیاه | هرس‌کنندگان و شاخه‌زن‌های درختان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخنرانی | درک مطلب خواندن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زیست‌شناسی | امور اداری و مدیریت | زبان انگلیسی | مکانیک | تولید غذا | ریاضیات</t>
+          <t>تولید و فرآوری | زیست‌شناسی | مدیریت و اداره | زبان انگلیسی | مکانیک | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک شفاهی | بینایی نزدیک | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال استقرایی | وضوح گفتار | بینایی دور | قدرت ایستا | هماهنگی چند عضو | زبردستی انگشتان | زبردستی دستی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی</t>
+          <t>حساسیت به مسئله | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک شفاهی | بینایی نزدیک | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال استقرایی | وضوح گفتار | بینایی دور | قدرت ایستا | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای پیاده‌روی یا دویدن | در معرض دمای بسیار گرم یا سرد | فضای باز، زیر سقف | کار با یا مشارکت در یک گروه کاری یا تیم | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | دفعات تصمیم‌گیری | نزدیکی فیزیکی | سلامت و ایمنی سایر کارگران | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، زیر سقف | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | پرورش‌دهندگان حیوانات | مراقبان حیوانات | دانشمندان علوم دامی | خریداران و ماموران خرید محصولات کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | کارگران ماهیگیری و شکار | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندی‌کنندگان و سورترهای محصولات کشاورزی | کارگران کمکی--کارگران تولید | کارگران ساده و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کنترل‌کنندگان، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش‌ها، پوشش گیاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی, فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | سلاخ‌ها و بسته‌بندی‌کنندگان گوشت</t>
+          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | پرورش‌دهندگان حیوانات | مراقبان حیوانات | دانشمندان علوم دامی | خریداران و نمایندگان خرید، محصولات کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | کارگران ماهیگیری و شکار | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | کمک‌کاران--کارگران تولید | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بندهای دستی | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | ذبح‌کنندگان و بسته‌بندندگان گوشت</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت مکانیزه تعمیر و نگهداری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخنرانی</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید غذا | مکانیک | زیست‌شناسی | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | امور اداری و مدیریت</t>
+          <t>تولید مواد غذایی | مکانیک | زیست‌شناسی | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان واکنش | حساسیت به مشکلات | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در خودروی روباز یا کار با تجهیزات | در معرض دمای بسیار گرم یا سرد | صرف زمان به صورت ایستاده | صرف زمان برای پیاده‌روی یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | اپراتورهای تجهیزات کشاورزی | درجه‌بندی‌کنندگان و سورترهای محصولات کشاورزی | پرورش‌دهندگان حیوانات | بازرسان کشاورزی | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | کارگران ماهیگیری و شکار | کارگران جنگل و حفاظت | کارگران محوطه‌سازی و فضای سبز | کنترل‌کنندگان، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش‌ها، پوشش گیاهی | کشاورزان، دامداران و سایر مدیران کشاورزی | تکنسین‌های کشاورزی | تکنسین‌های کشاورزی دقیق | مراقبان حیوانات | سازندگان دسته‌ای مواد غذایی | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کارگران ساده و جابجا‌کنندگان دستی بار، کالا و مواد | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | پیمانکاران کارگر کشاورزی</t>
+          <t>کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | اپراتورهای تجهیزات کشاورزی | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | پرورش‌دهندگان حیوانات | بازرسان کشاورزی | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | کارگران ماهیگیری و شکار | کارگران جنگل و حفاظت | کارگران فضای سبز و نگهداری محوطه | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | کشاورزان، دامداران و سایر مدیران کشاورزی | تکنسین‌های کشاورزی | تکنسین‌های کشاورزی دقیق | مراقبان حیوانات | بچ‌سازان مواد غذایی | بسته‌بندهای دستی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | پیمانکاران نیروی کار کشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنرانی</t>
+          <t>تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>جغرافیا | مکانیک | قانون و حکومت | خدمات مشتریان و پرسنل | زیست‌شناسی | زبان انگلیسی | فروش و بازاریابی | آموزش و تربیت</t>
+          <t>جغرافیا | مکانیک | قانون و دولت | خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | فروش و بازاریابی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>جهت‌یابی فضایی | بینایی دور | قدرت ایستا | انعطاف‌پذیری بستار | بینایی نزدیک | قدرت تنه | ثبات دست و بازو | استدلال استقرایی | حساسیت به مشکلات | زبردستی دستی | دقت کنترل | هماهنگی چند عضو | درک عمق | درک شفاهی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | قدرت پویا | زمان واکنش | وضوح گفتار | حساسیت شنوایی | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی</t>
+          <t>جهت‌گیری فضایی | بینایی دور | قدرت ایستا | انعطاف‌پذیری بستار | بینایی نزدیک | قدرت تنه | ثبات دست و بازو | استدلال استقرایی | حساسیت به مسئله | مهارت دستی | دقت کنترل | هماهنگی چند عضو | درک عمق | درک شفاهی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | قدرت پویا | زمان عکس‌العمل | وضوح گفتار | حساسیت شنوایی | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | در معرض شرایط نوری بسیار روشن یا نامناسب | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | سطح رقابت | در معرض دمای بسیار گرم یا سرد | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | نزدیکی فیزیکی | فضاهای داخلی، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | سطح رقابت | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | ناخداها، افسران دوم و خلبانان شناورهای آبی | غواصان تجاری | اپراتورهای جرثقیل و دکل | اپراتورهای لایروب | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | محیط‌بانان صید و شکار | کارگران جنگل و حفاظت | کارگران کمکی--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای کامیون صنعتی و تراکتور | کارگران ساده و جابجا‌کنندگان دستی بار, کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورهای قایق موتوری | دکل‌بندها | ملوانان و روغن‌کاران دریایی | مهندسان کشتی</t>
+          <t>اپراتورهای تجهیزات کشاورزی | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | غواصان تجاری | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | محیط‌بانان و جنگل‌بانان | کارگران جنگل و حفاظت | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورهای قایق موتوری | ریگرها | ملوانان و روغن‌کاران دریایی | مهندسان کشتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده | ESRI ArcGIS software | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | IBM Lotus 1-2-3 | IBM Lotus Notes | Leica Geosystems ERDAS IMAGINE | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | IBM Lotus 1-2-3 | IBM Lotus Notes | Leica Geosystems ERDAS IMAGINE | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخنرانی | گوش دادن فعال | درک مطلب خواندن</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و پرسنل | امور اداری و مدیریت | جغرافیا | زیست‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | جغرافیا | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | درک شفاهی | بیان شفاهی | قدرت ایستا | استدلال قیاسی | بینایی دور | بینایی نزدیک | استقامت | قدرت تنه | قدرت پویا | هماهنگی چند عضو | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | درک عمق | دقت کنترل | زبردستی انگشتان | زبردستی دستی | ثبات دست و بازو | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک کتبی</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | قدرت ایستا | استدلال قیاسی | بینایی دور | بینایی نزدیک | استقامت | قدرت تنه | قدرت پویا | هماهنگی چند عضو | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | درک عمق | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | دفعات تصمیم‌گیری | در معرض دمای بسیار گرم یا سرد | فضاهای داخلی، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض آلاینده‌ها | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | سلامت و ایمنی سایر کارگران | در معرض تجهیزات خطرناک | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، از جمله بهداشت | قطع‌کنندگان درختان | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | آتش‌نشانان | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول کارگران محوطه‌سازی، خدمات چمن و فضای سبز | محیط‌بانان صید و شکار | بازرسان آتش‌سوزی جنگل و متخصصان پیشگیری | تکنسین‌های جنگل و حفاظت | جنگلبانان | کارگران محوطه‌سازی و فضای سبز | کنترل‌کنندگان، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش‌ها، پوشش گیاهی | مدیران مرتع | دانشمندان خاک و گیاه | هرس‌کنندگان و آرایش‌دهندگان درختان | اپراتورهای تصفیه‌خانه و سیستم آب و فاضلاب</t>
+          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت | برنامه‌ریزان احیای محیط‌زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | قطع‌کنندگان درختان | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | آتش‌نشانان | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | محیط‌بانان و جنگل‌بانان | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | کارگران فضای سبز و نگهداری محوطه | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | مدیران مراتع | دانشمندان خاک و گیاه | هرس‌کنندگان و شاخه‌زن‌های درختان | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>زمان واکنش | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | سرعت حرکت اعضا | زبردستی دستی | ثبات دست و بازو | توجه شنوایی | درک عمق | هماهنگی کلی بدن | استقامت | قدرت تنه | بینایی نزدیک | بینایی دور | تشخیص رنگ بصری | حساسیت شنوایی | انعطاف‌پذیری دامنه حرکت | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | حساسیت به مشکلات | کنترل نرخ | جهت‌دهی پاسخ | تجسم | تعادل کلی بدن | قدرت پویا | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک شفاهی</t>
+          <t>زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | سرعت حرکت اعضا | مهارت دستی | ثبات دست و بازو | توجه شنیداری | درک عمق | هماهنگی کلی بدن | استقامت | قدرت تنه | بینایی نزدیک | بینایی دور | تشخیص رنگ بصری | حساسیت شنوایی | انعطاف‌پذیری دامنه حرکت | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | کنترل نرخ | جهت‌گیری پاسخ | تجسم | تعادل کلی بدن | قدرت پویا | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض تجهیزات خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت ایستاده | در معرض آلاینده‌ها | دفعات تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض ارتعاش کل بدن | صرف زمان برای خم کردن یا چرخاندن بدن | اهمیت دقیق یا دقیق بودن | صرف زمان برای پیاده‌روی یا دویدن | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | صرف زمان برای انجام حرکات تکراری | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان برای خم کردن یا چرخاندن بدن | اهمیت دقیق یا درست بودن | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | نجاران | حفاران زمین، به جز نفت و گاز | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگلبانان | کارگران کمکی--کارگران استخراج | اپراتورهای بالابر و وینچ | کارگران محوطه‌سازی و فضای سبز | درجه‌بندی‌کنندگان و ارزیابان چوب | اپراتورهای تجهیزات چوب‌بری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | دکل‌بندها | سنگ‌شکنان، معدن سنگ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی، چوب | هرس‌کنندگان و آرایش‌دهندگان درختان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نجاری، به جز اره‌کشی</t>
+          <t>اپراتورهای تجهیزات کشاورزی | نجّاران | حفاران زمین، به جز نفت و گاز | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | کارگران فضای سبز و نگهداری محوطه | درجه‌بندی‌کنندگان و ارزیابان چوب | اپراتورهای تجهیزات چوب‌بری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | ریگرها | سنگ‌شکنان معدن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | هرس‌کنندگان و شاخه‌زن‌های درختان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دقت کنترل | زمان واکنش | هماهنگی چند عضو | ثبات دست و بازو | درک عمق | جهت‌دهی پاسخ | حساسیت به مشکلات | بینایی دور | کنترل نرخ | بینایی نزدیک | زبردستی دستی | تجسم | سرعت ادراکی | تشخیص رنگ بصری | قدرت تنه | زبردستی انگشتان | توجه انتخابی | جهت‌یابی فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | زمان عکس‌العمل | هماهنگی چند عضو | ثبات دست و بازو | درک عمق | جهت‌گیری پاسخ | حساسیت به مسئله | بینایی دور | کنترل نرخ | بینایی نزدیک | مهارت دستی | تجسم | سرعت ادراکی | تشخیص رنگ بصری | قدرت تنه | مهارت انگشتان | توجه انتخابی | جهت‌گیری فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | دفعات تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | پیامد خطا | مکالمات تلفنی | آزادی در تصمیم‌گیری | در معرض ارتعاش کل بدن | پیامدهای کاری و نتایج سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | اهمیت دقیق یا دقیق بودن | اهمیت تکرار وظایف یکسان | در معرض تجهیزات خطرناک | در معرض آلاینده‌ها</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | پیامد خطا | مکالمات تلفنی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض ارتعاش کل بدن | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین‌های استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و دکل | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن سطحی | قطع‌کنندگان درختان | کارگران کمکی--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای کامیون صنعتی و تراکتور | اپراتورهای ماشین‌های بارگیری و انتقال، معدن زیرزمینی | درجه‌بندی‌کنندگان و ارزیابان چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاست | مکانیک‌های تجهیزات سنگین سیار، به جز موتور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | کارگران ساده، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی، چوب | بارگیری‌کنندگان واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نجاری، به جز اره‌کشی</t>
+          <t>اپراتورهای تجهیزات کشاورزی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | قطع‌کنندگان درختان | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | درجه‌بندی‌کنندگان و ارزیابان چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | کارگران فنی همه‌کاره نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | بارگیران واگن مخزنی، کامیون و کشتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخنرانی | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | ریاضیات | خدمات مشتریان و پرسنل | امور اداری و مدیریت</t>
+          <t>تولید و فرآوری | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مشکلات | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | زبردستی انگشتان | زبردستی دستی | ثبات دست و بازو | توجه انتخابی | سهولت کار با اعداد | استدلال ریاضی | ترتیب‌دهی اطلاعات | درک کتبی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | توانایی عددی | استدلال ریاضی | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | دفعات تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا دقیق بودن | در معرض تجهیزات خطرناک | در معرض دمای بسیار گرم یا سرد | فشار زمانی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | فضاهای داخلی، بدون کنترل شرایط محیطی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | محیط داخلی، بدون کنترل شرایط محیطی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکنندگان ساختار، سطوح، دکل‌بندی و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کن | قطع‌کنندگان درختان | اپراتورها و متصدیان کوره، کوره پخت، اجاق، خشک‌کن و دیگ | درجه‌بندی‌کنندگان و سورترهای محصولات کشاورزی | کارگران پرداخت و صیقل‌کاری، دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری، فلز و پلاستیک | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارگران ساده و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای تجهیزات چوب‌بری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاست | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی | تیزکنندگان و پرداخت‌کنندگان ابزار | توزین‌کنندگان، اندازه‌گیران، بررسی‌کنندگان و نمونه‌برداران، ثبت اطلاعات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نجاری، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | قطع‌کنندگان درختان | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای تجهیزات چوب‌بری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | بسته‌بندهای دستی | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی کالا | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت مکانیزه تعمیر و نگهداری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخنرانی</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | زیست‌شناسی | ترابری | ریاضیات</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | زیست‌شناسی | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان واکنش | حساسیت به مشکلات | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دمای بسیار گرم یا سرد | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا دقیق بودن | پیامد خطا | صرف زمان برای پیاده‌روی یا دویدن | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | در معرض ارتعاش کل بدن | در خودروی روباز یا کار با تجهیزات</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض ارتعاش کل بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>قطع‌کنندگان درختان | اپراتورهای تجهیزات چوب‌بری | درجه‌بندی‌کنندگان و ارزیابان چوب | کارگران جنگل و حفاظت | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | تکنسین‌های جنگل و حفاظت | هرس‌کنندگان و آرایش‌دهندگان درختان | جنگلبانان | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | رانندگان کامیون‌های سنگین و تریلر | اپراتورهای جرثقیل و دکل | اپراتورهای بالابر و وینچ | کارگران ساختمانی | دکل‌بندها | مکانیک‌های تجهیزات سنگین سیار، به جز موتور | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی، چوب | کارگران ساده و جابجا‌کنندگان دستی بار، کالا و مواد | دانشمندان حفاظت | اپراتورهای تجهیزات کشاورزی | اپراتورهای کامیون صنعتی و تراکتور</t>
+          <t>قطع‌کنندگان درختان | اپراتورهای تجهیزات چوب‌بری | درجه‌بندی‌کنندگان و ارزیابان چوب | کارگران جنگل و حفاظت | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | تکنسین‌های جنگل و حفاظت | هرس‌کنندگان و شاخه‌زن‌های درختان | جنگل‌بانان | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای جرثقیل و تاور | اپراتورهای بالابر و وینچ | کارگران ساختمانی | ریگرها | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | دانشمندان حفاظت | اپراتورهای تجهیزات کشاورزی | اپراتورهای تراکتور و کامیون صنعتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Autodesk AutoCAD | FranklinCovey TabletPlanner | نرم‌افزار گرافیک | HCSS HeavyJob | نرم‌افزار ردیابی موجودی | Mi-Co Mi-Forms | Microsoft Excel | Microsoft NetMeeting | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera P6 Enterprise Portfolio Project Management | Oracle Primavera Systems | Procore software | Prolog | QuickBase business management software | Sage 300 Construction and Real Estate | نرم‌افزار زمان‌بندی</t>
+          <t>Adobe Acrobat | Autodesk AutoCAD | FranklinCovey TabletPlanner | نرم‌افزار گرافیکی | HCSS HeavyJob | نرم‌افزار ردیابی موجودی | Mi-Co Mi-Forms | Microsoft Excel | Microsoft NetMeeting | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera P6 Enterprise Portfolio Project Management | Oracle Primavera Systems | Procore software | Prolog | نرم‌افزار مدیریت کسب‌وکار QuickBase | Sage 300 Construction and Real Estate | نرم‌افزار زمان‌بندی</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخنرانی | تفکر انتقادی | درک مطلب خواندن | نظارت | استراتژی‌های یادگیری | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>امور اداری و مدیریت | ساخت و ساز ساختمان | مکانیک | خدمات مشتریان و پرسنل | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | پرسنل و منابع انسانی</t>
+          <t>مدیریت و اداره | ساختمان و ساخت‌وساز | مکانیک | خدمات مشتری و شخصی | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | درک کتبی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | بینایی دور | زبردستی دستی | توجه انتخابی | دقت کنترل | زبردستی انگشتان | اشتراک زمانی | تجسم | سرعت ادراکی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | درک کتبی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | بینایی دور | مهارت دستی | توجه انتخابی | دقت کنترل | مهارت انگشتان | تقسیم توجه | تجسم | سرعت ادراکی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | دفعات تصمیم‌گیری | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | پیامدهای کاری و نتایج سایر کارگران | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا دقیق بودن | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض دمای بسیار گرم یا سرد | در معرض تجهیزات خطرناک | فشار زمانی | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در معرض آلاینده‌ها | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | صرف زمان به صورت ایستاده | در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | پیامدهای کاری و نتایج سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | صرف زمان برای ایستادن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مدیران ساخت و ساز | بازرسان ساختمان و ساخت و ساز | برق‌کاران | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول کارگران کمکی، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران محوطه‌سازی، خدمات چمن و فضای سبز | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکنندگان | سرپرستان خط اول کارمندان پشتیبانی اداری و دفتری | سرپرستان خط اول مهمانداران مسافران | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارگران امنیتی | مدیران کل و عملیاتی | کارگران کمکی--برق‌کاران | مهندسان صنایع | کارگران نگهداری و تعمیرات، عمومی | مدیران نصب انرژی خورشیدی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی عمران | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | برق‌کاران | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | دستیاران--برق‌کاران | مهندسان صنایع | کارگران نگهداری و تعمیرات عمومی | مدیران نصب انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0071_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0071_fa.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استحکام تنه | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه‌ای | چابکی دستی | هماهنگی چنداندامی | چابکی انگشتان | قدرت ایستا | قدرت پویا | کنترل نرخ | دید نزدیک | استقامت عضلانی | قدرت انفجاری | بیان شفاهی | زمان واکنش | درک شفاهی | دید دور | هماهنگی کلی بدن | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>قدرت تنه | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه حرکت | مهارت دستی | هماهنگی چند عضو | مهارت انگشتان | قدرت ایستا | قدرت پویا | کنترل نرخ | بینایی نزدیک | استقامت | قدرت انفجاری | بیان شفاهی | زمان عکس‌العمل | درک شفاهی | بینایی دور | هماهنگی کلی بدن | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های خردایش، سنگ‌زنی و پرداخت | درخت‌اندازان و چوب‌بُران جنگل | مدیران کشاورزی، دامپروری و سایر امور زراعی | کارگران دامداری، مرغداری و آبزی‌پروری | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | متصدیان ترکیب و پخت فرمولاسیون مواد غذایی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن صنایع غذایی و دخانیات | کارگران جنگل‌داری و حفاظت از منابع طبیعی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | کارگران حمل، بارگیری و جابه‌جایی دستی بار | کارگران فضای سبز و باغبانی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات صنعتی | قصابان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بنداران و کارگران بسته‌بندی دستی | سم‌پاشان و متصدیان کنترل شیمیایی آفات گیاهی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی و تقطیر | دانشمندان و پژوهشگران خاک و علوم گیاهی | هرس‌کاران و پیرایندگان درختان</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | درخت‌اندازان و چوب‌بُران جنگل | مدیران امور کشاورزی، دامپروری و شیلات | کارگران پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران باغبانی، فضای سبز و نگهداری محوطه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | کارگران بسته‌بندی دستی | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | متخصصان خاک‌شناسی و علوم گیاهی | هرس‌کنندگان و پیرایندگان درختان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و پردازش | زیست‌شناسی | مدیریت و امور اداری | زبان انگلیسی | مکانیک | تولید مواد غذایی | ریاضیات</t>
+          <t>تولید و فرآوری | زیست‌شناسی | مدیریت و اداره | زبان انگلیسی | مکانیک | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک شفاهی | دید نزدیک | استحکام تنه | مرتب‌سازی اطلاعات | استدلال استقرایی | وضوح گفتار | دید دور | قدرت ایستا | هماهنگی چنداندامی | چابکی انگشتان | چابکی دستی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | درک کتبی</t>
+          <t>حساسیت به مسئله | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک شفاهی | بینایی نزدیک | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال استقرایی | وضوح گفتار | بینایی دور | قدرت ایستا | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | اصلاح‌نژادکنندگان و پرورش‌دهندگان دام | تیمارداران و مراقبان حیوانات | کارشناسان علوم دامی | مأموران خرید و تدارکات محصولات کشاورزی و دامی | مدیران کشاورزی، دامپروری و سایر امور زراعی | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | کارگران صیادی و شکار | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن صنایع غذایی و دخانیات | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | کارگران کمکی و ساده خطوط تولید | کارگران حمل، بارگیری و جابه‌جایی دستی بار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات صنعتی | قصابان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بنداران و کارگران بسته‌بندی دستی | سم‌پاشان و متصدیان کنترل شیمیایی آفات گیاهی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی و تقطیر | سلاخان و بسته‌بندی‌کنندگان گوشت</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | مراقبان و نگهداران حیوانات | متخصصان علوم دامی | خریداران و کارشناسان خرید محصولات کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | صیادان، ماهیگیران و شکارچیان | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کمک‌کارگران خطوط تولید | کارگران جابه‌جایی دستی بار، کالا و مصالح | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | کارگران بسته‌بندی دستی | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | قصابان و بسته‌بندی‌کنندگان گوشت</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | مکانیک | زیست‌شناسی | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | مدیریت و امور اداری</t>
+          <t>تولید مواد غذایی | مکانیک | زیست‌شناسی | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | استحکام تنه | استقامت عضلانی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه‌ای | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران زراعت، نهالستان و گلخانه | کارگران دامداری، مرغداری و آبزی‌پروری | اپراتورهای ماشین‌آلات و ادوات کشاورزی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | اصلاح‌نژادکنندگان و پرورش‌دهندگان دام | بازرسان محصولات و فرآورده‌های کشاورزی | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | کارگران صیادی و شکار | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران فضای سبز و باغبانی | سم‌پاشان و متصدیان کنترل شیمیایی آفات گیاهی | مدیران کشاورزی، دامپروری و سایر امور زراعی | تکنسین‌های کشاورزی | تکنسین‌های کشاورزی دقیق | تیمارداران و مراقبان حیوانات | متصدیان ترکیب و پخت فرمولاسیون مواد غذایی | بسته‌بنداران و کارگران بسته‌بندی دستی | کارگران حمل، بارگیری و جابه‌جایی دستی بار | مکانیک‌ها و تعمیرکاران ماشین‌آلات و ادوات کشاورزی | پیمانکاران تأمین نیروی کار کشاورزی</t>
+          <t>کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | اپراتورهای ماشین‌آلات و ادوات کشاورزی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | بازرسان محصولات و فرآورده‌های کشاورزی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | صیادان، ماهیگیران و شکارچیان | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | مدیران امور کشاورزی، دامپروری و شیلات | تکنسین‌های کشاورزی | تکنسین‌های کشاورزی دقیق | مراقبان و نگهداران حیوانات | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | کارگران بسته‌بندی دستی | کارگران جابه‌جایی دستی بار، کالا و مصالح | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | پیمانکاران و تأمین‌کنندگان نیروی کار کشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>جغرافیا | مکانیک | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | زبان انگلیسی | فروش و بازاریابی | آموزش و تدریس</t>
+          <t>جغرافیا | مکانیک | قانون و دولت | خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | فروش و بازاریابی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>جهت‌یابی فضایی | دید دور | قدرت ایستا | انعطاف‌پذیری بستار | دید نزدیک | استحکام تنه | ثبات دست و بازو | استدلال استقرایی | حساسیت به مسئله | چابکی دستی | دقت کنترل | هماهنگی چنداندامی | ادراک عمق | درک شفاهی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دامنه‌ای | قدرت پویا | زمان واکنش | وضوح گفتار | حساسیت شنوایی | تمایز رنگ‌ها | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>جهت‌گیری فضایی | بینایی دور | قدرت ایستا | انعطاف‌پذیری بستار | بینایی نزدیک | قدرت تنه | ثبات دست و بازو | استدلال استقرایی | حساسیت به مسئله | مهارت دستی | دقت کنترل | هماهنگی چند عضو | درک عمق | درک شفاهی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | قدرت پویا | زمان عکس‌العمل | وضوح گفتار | حساسیت شنوایی | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | کاپیتان‌ها، افسران اول و ناوبُران شناورهای دریایی | غواصان تجاری و صنعتی | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | کارگران زراعت، نهالستان و گلخانه | کارگران دامداری، مرغداری و آبزی‌پروری | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | محیط‌بانان و مأموران حفاظت شیلات و شکاربانی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران کمکی در عملیات استخراج | اپراتورهای بالابر و وینچ | رانندگان لیفتراک و تراکتورهای صنعتی | کارگران حمل، بارگیری و جابه‌جایی دستی بار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات صنعتی | قصابان و پاک‌کنندگان گوشت، مرغ و ماهی | قایق‌رانان شناورهای موتوری | باربندان و ریگرها | ملوانان و روغن‌کاران موتورخانه شناور | مهندسان کشتی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | غواصان تجاری و صنعتی | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | قایقرانان قایق‌های موتوری | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | جغرافیا | زیست‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | جغرافیا | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | قدرت ایستا | استدلال قیاسی | دید دور | دید نزدیک | استقامت عضلانی | استحکام تنه | قدرت پویا | هماهنگی چنداندامی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | ادراک عمق | دقت کنترل | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | درک کتبی</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | قدرت ایستا | استدلال قیاسی | بینایی دور | بینایی نزدیک | استقامت | قدرت تنه | قدرت پویا | هماهنگی چند عضو | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | درک عمق | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | کارشناسان حفاظت از خاک و منابع طبیعی | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | درخت‌اندازان و چوب‌بُران جنگل | کارگران زراعت، نهالستان و گلخانه | آتش‌نشانان | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | سرپرستان رده‌اول کارگران باغبانی، فضای سبز و نگهداری محوطه | محیط‌بانان و مأموران حفاظت شیلات و شکاربانی | بازرسان و کارشناسان پیشگیری از حریق جنگل | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان و مهندسان جنگل‌داری | کارگران فضای سبز و باغبانی | سم‌پاشان و متصدیان کنترل شیمیایی آفات گیاهی | مدیران مراتع و چراگاه‌ها | دانشمندان و پژوهشگران خاک و علوم گیاهی | هرس‌کاران و پیرایندگان درختان | اپراتورها و متصدیان تصفیه‌خانه‌های آب و فاضلاب</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | درخت‌اندازان و چوب‌بُران جنگل | کارگران زراعت، نهالستان و گلخانه | آتش‌نشانان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی | هرس‌کنندگان و پیرایندگان درختان | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | ریاضیات | تولید و پردازش</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>زمان واکنش | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | سرعت حرکت اندام‌ها | چابکی دستی | ثبات دست و بازو | توجه شنیداری | ادراک عمق | هماهنگی کلی بدن | استقامت عضلانی | استحکام تنه | دید نزدیک | دید دور | تمایز رنگ‌ها | حساسیت شنوایی | انعطاف‌پذیری دامنه‌ای | انعطاف‌پذیری بستار | مرتب‌سازی اطلاعات | حساسیت به مسئله | کنترل نرخ | جهت‌دهی پاسخ | تجسم فضایی | تعادل کلی بدن | قدرت پویا | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | درک شفاهی</t>
+          <t>زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | سرعت حرکت اعضا | مهارت دستی | ثبات دست و بازو | توجه شنیداری | درک عمق | هماهنگی کلی بدن | استقامت | قدرت تنه | بینایی نزدیک | بینایی دور | تشخیص رنگ بصری | حساسیت شنوایی | انعطاف‌پذیری دامنه حرکت | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | کنترل نرخ | جهت‌گیری پاسخ | تجسم | تعادل کلی بدن | قدرت پویا | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | نجاران | حفاران زمین، به‌جز چاه‌های نفت و گاز | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان و مهندسان جنگل‌داری | کارگران کمکی در عملیات استخراج | اپراتورهای بالابر و وینچ | کارگران فضای سبز و باغبانی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | اپراتورهای ماشین‌آلات مکانیزه چوب‌بری و جنگل‌داری | اپراتورهای ماشین‌آلات راه‌سازی و تجهیزات عمرانی | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | باربندان و ریگرها | سنگ‌شکنان و سنگ‌بران معادن | تنظیم‌کنندگان و اپراتورهای ماشین‌های اره‌کشی چوب | هرس‌کاران و پیرایندگان درختان | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات فرآوری چوب، به‌جز اره‌کشی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | نجاران و درودگران | حفاران زمین، به‌جز نفت و گاز | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | کارگران باغبانی، فضای سبز و نگهداری محوطه | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | سنگ‌شکنان و برش‌کاران سنگ معدن | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | هرس‌کنندگان و پیرایندگان درختان | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | تولید و پردازش</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دقت کنترل | زمان واکنش | هماهنگی چنداندامی | ثبات دست و بازو | ادراک عمق | جهت‌دهی پاسخ | حساسیت به مسئله | دید دور | کنترل نرخ | دید نزدیک | چابکی دستی | تجسم فضایی | سرعت ادراک | تمایز رنگ‌ها | استحکام تنه | چابکی انگشتان | توجه انتخابی | جهت‌یابی فضایی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | زمان عکس‌العمل | هماهنگی چند عضو | ثبات دست و بازو | درک عمق | جهت‌گیری پاسخ | حساسیت به مسئله | بینایی دور | کنترل نرخ | بینایی نزدیک | مهارت دستی | تجسم | سرعت ادراکی | تشخیص رنگ بصری | قدرت تنه | مهارت انگشتان | توجه انتخابی | جهت‌گیری فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین‌آلات استخراج پیوسته معادن | اپراتورها و متصدیان نوار نقاله و خطوط انتقال | اپراتورهای جرثقیل و تاورکرین | حفاران زمین، به‌جز چاه‌های نفت و گاز | اپراتورهای بیل مکانیکی، دراگ‌لاین و تجهیزات بارگیری معادن سطحی | درخت‌اندازان و چوب‌بُران جنگل | کارگران کمکی در عملیات استخراج | اپراتورهای بالابر و وینچ | رانندگان لیفتراک و تراکتورهای صنعتی | اپراتورهای ماشین‌آلات بارگیری و باربری معادن زیرزمینی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | تنظیم‌کنندگان و اپراتورهای فرز و رنده صنایع فلزی و پلاستیک | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات راه‌سازی و تجهیزات عمرانی | کارگران دکل و محوطه تأسیسات نفت و گاز | تنظیم‌کنندگان و اپراتورهای ماشین‌های اره‌کشی چوب | متصدیان بارگیری مخازن واگن، تانکر و شناور | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات فرآوری چوب، به‌جز اره‌کشی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | درخت‌اندازان و چوب‌بُران جنگل | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | کارگران عمومی سکو و میادین نفت و گاز | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و پردازش | ریاضیات | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>تولید و فرآوری | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | دید دور | سرعت ادراک | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | تمایز رنگ‌ها | دقت کنترل | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | کار با اعداد | استدلال ریاضی | مرتب‌سازی اطلاعات | درک کتبی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | توانایی عددی | استدلال ریاضی | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌آلات چسب‌زنی و اتصال | مونتاژکاران سازه، سطوح، مهارها و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های خردایش، سنگ‌زنی و پرداخت | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات برش و اسلایس چوب | درخت‌اندازان و چوب‌بُران جنگل | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت صنعتی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | پرداخت‌کاران و صیقل‌کاران دستی سطوح | تنظیم‌کنندگان و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت و لپینگ فلز و پلاستیک | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و متصدیان توزین | کارگران حمل، بارگیری و جابه‌جایی دستی بار | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای فرز و رنده صنایع فلزی و پلاستیک | بسته‌بنداران و کارگران بسته‌بندی دستی | کارمندان برنامه‌ریزی، تولید و تسریع سفارش‌ها | کارمندان انبار، بارگیری و دریافت کالا | تیزکاران و سنگ‌زن‌های ابزار و اره‌ها | متصدیان توزین، ابعادبرداری، کنترل و ثبت اطلاعات بار | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات فرآوری چوب، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | درخت‌اندازان و چوب‌بُران جنگل | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | کارگران بسته‌بندی دستی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارمندان انبار، ارسال و دریافت کالا | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و پردازش | زیست‌شناسی | حمل‌ونقل | ریاضیات</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | زیست‌شناسی | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | استحکام تنه | استقامت عضلانی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه‌ای | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>درخت‌اندازان و چوب‌بُران جنگل | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | کارگران جنگل‌داری و حفاظت از منابع طبیعی | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | هرس‌کاران و پیرایندگان درختان | کارشناسان و مهندسان جنگل‌داری | اپراتورهای ماشین‌آلات راه‌سازی و تجهیزات عمرانی | رانندگان تریلر و کامیون‌های سنگین جاده‌ای | اپراتورهای جرثقیل و تاورکرین | اپراتورهای بالابر و وینچ | کارگران ساختمانی و عمرانی | باربندان و ریگرها | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | تنظیم‌کنندگان و اپراتورهای ماشین‌های اره‌کشی چوب | کارگران حمل، بارگیری و جابه‌جایی دستی بار | دانشمندان و کارشناسان حفاظت از منابع طبیعی | اپراتورهای ماشین‌آلات و ادوات کشاورزی | رانندگان لیفتراک و تراکتورهای صنعتی</t>
+          <t>درخت‌اندازان و چوب‌بُران جنگل | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | کارگران جنگل‌داری و حفاظت از منابع طبیعی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | هرس‌کنندگان و پیرایندگان درختان | کارشناسان جنگل‌داری و جنگل‌بانان | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | رانندگان خودروهای سنگین و کشنده‌ها | اپراتورهای جرثقیل و تاورکرین | اپراتورهای بالابر و وینچ | کارگران ساختمانی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | مکانیک تجهیزات سنگین متحرک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | کارگران جابه‌جایی دستی بار، کالا و مصالح | دانشمندان حفاظت از منابع طبیعی | اپراتورهای ماشین‌آلات و ادوات کشاورزی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ساختمان و سازه | مکانیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | امور اداری و منابع انسانی</t>
+          <t>مدیریت و اداره | ساختمان و ساخت‌وساز | مکانیک | خدمات مشتری و شخصی | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | استدلال قیاسی | وضوح گفتار | درک کتبی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | دید دور | چابکی دستی | توجه انتخابی | دقت کنترل | چابکی انگشتان | اشتراک زمانی | تجسم فضایی | سرعت ادراک | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | درک کتبی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | بینایی دور | مهارت دستی | توجه انتخابی | دقت کنترل | مهارت انگشتان | تقسیم توجه | تجسم | سرعت ادراکی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی عمران | مدیران پروژه‌های ساختمانی و عمرانی | بازرسان فنی ساختمان و سازه | برق‌کاران صنعتی و ساختمانی | سرپرستان رده‌اول کارکنان خدمات سرگرمی و تفریحی، به‌جز امور شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | سرپرستان رده‌اول کارگران کمکی، باربری و جابه‌جایی دستی بار | سرپرستان رده‌اول کارکنان خدمات و نظافت اماکن | سرپرستان رده‌اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول تعمیرکاران، نصابان و مکانیک‌ها | سرپرستان رده‌اول کارکنان امور دفتری و پشتیبانی اداری | سرپرستان رده‌اول خدمه و مهمانداران مسافری | سرپرستان رده‌اول کارگران خطوط تولید و عملیات | سرپرستان رده‌اول نیروهای حراست و انتظامات | مدیران اجرایی و مدیران عملیات | کارگران کمکی برق‌کاران | مهندسان صنایع | کارشناسان و تعمیرکاران فنی عمومی | مدیران پروژه‌های نصب سامانه‌های انرژی خورشیدی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | برق‌کاران | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | کمک‌برق‌کاران | مهندسان صنایع | کارگران عمومی تعمیرات و نگهداری تاسیسات | مدیران اجرای پروژه‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
